--- a/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 5,95</t>
+          <t>-10,24; 5,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 0,92</t>
+          <t>-14,29; 0,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,97; -0,52</t>
+          <t>-14,65; -0,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,4</t>
+          <t>-3,93; 10,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,24; 1,52</t>
+          <t>-11,68; 1,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,9; 20,0</t>
+          <t>-12,45; 18,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 6,17</t>
+          <t>-4,52; 6,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; -0,88</t>
+          <t>-10,81; -0,98</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 8,0</t>
+          <t>-11,43; 6,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,4; 43,98</t>
+          <t>-44,82; 41,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-62,14; 10,9</t>
+          <t>-64,22; 6,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,53; 0,57</t>
+          <t>-68,56; -5,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,13; 94,42</t>
+          <t>-22,56; 89,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,56; 14,28</t>
+          <t>-65,77; 10,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 160,72</t>
+          <t>-81,09; 149,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,39; 43,93</t>
+          <t>-25,0; 43,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,76; -6,36</t>
+          <t>-57,47; -5,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,06; 71,08</t>
+          <t>-63,81; 49,45</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 5,22</t>
+          <t>-8,92; 4,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,37; -1,98</t>
+          <t>-13,47; -1,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,07; -5,76</t>
+          <t>-18,18; -6,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 4,34</t>
+          <t>-6,68; 4,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 4,67</t>
+          <t>-6,22; 4,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,2; 7,29</t>
+          <t>-6,33; 6,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 2,76</t>
+          <t>-5,7; 2,91</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,32; -0,05</t>
+          <t>-8,31; -0,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,1; -0,92</t>
+          <t>-10,32; -0,9</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,65; 28,74</t>
+          <t>-34,82; 25,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,81; -9,51</t>
+          <t>-53,81; -7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,27; -28,87</t>
+          <t>-71,8; -31,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,07; 34,4</t>
+          <t>-36,94; 36,38</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,47; 35,35</t>
+          <t>-34,47; 35,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,25; 56,86</t>
+          <t>-36,44; 55,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,65; 16,71</t>
+          <t>-27,26; 19,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,55; 0,91</t>
+          <t>-40,15; -0,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,66; -4,36</t>
+          <t>-50,89; -4,59</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,68; 0,71</t>
+          <t>-14,48; 0,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-15,84; -2,32</t>
+          <t>-17,34; -3,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,05; 39,57</t>
+          <t>-2,44; 37,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 4,73</t>
+          <t>-7,84; 5,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 4,53</t>
+          <t>-8,0; 4,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 10,74</t>
+          <t>-3,88; 10,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; 0,59</t>
+          <t>-8,78; 0,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,94; -1,17</t>
+          <t>-10,27; -0,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 26,53</t>
+          <t>0,16; 25,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,7; 4,5</t>
+          <t>-55,73; 4,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,14; -12,88</t>
+          <t>-66,82; -17,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 214,86</t>
+          <t>-11,95; 217,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 39,39</t>
+          <t>-43,38; 42,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 40,19</t>
+          <t>-43,05; 38,21</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 89,82</t>
+          <t>-21,9; 98,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-41,61; 4,32</t>
+          <t>-43,27; 5,23</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-47,95; -3,82</t>
+          <t>-51,07; -5,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 155,54</t>
+          <t>0,24; 160,52</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 10,55</t>
+          <t>-1,39; 10,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 10,65</t>
+          <t>-1,87; 10,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 6,97</t>
+          <t>-4,84; 6,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 2,45</t>
+          <t>-8,75; 1,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 6,88</t>
+          <t>-4,42; 6,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 4,52</t>
+          <t>-6,52; 4,43</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 4,91</t>
+          <t>-3,01; 4,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 7,22</t>
+          <t>-1,33; 7,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 3,73</t>
+          <t>-4,17; 3,71</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-13,44; 128,16</t>
+          <t>-9,6; 135,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 119,58</t>
+          <t>-13,07; 138,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 79,41</t>
+          <t>-34,34; 82,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,55; 26,59</t>
+          <t>-57,59; 18,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-27,37; 80,69</t>
+          <t>-30,45; 74,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,48; 49,6</t>
+          <t>-42,67; 49,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,49; 49,35</t>
+          <t>-22,55; 48,23</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,2; 72,02</t>
+          <t>-10,39; 71,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 38,67</t>
+          <t>-31,42; 37,44</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,52</t>
+          <t>-4,03; 2,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,84</t>
+          <t>-6,83; -0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,81</t>
+          <t>-5,34; 11,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,14</t>
+          <t>-4,37; 1,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,46</t>
+          <t>-4,07; 1,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,84</t>
+          <t>-3,77; 4,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,42</t>
+          <t>-3,11; 1,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,36</t>
+          <t>-4,94; -0,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,8</t>
+          <t>-3,31; 5,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 15,76</t>
+          <t>-21,07; 16,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -5,21</t>
+          <t>-36,26; -5,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 87,83</t>
+          <t>-28,94; 72,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 16,89</t>
+          <t>-27,57; 12,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 11,82</t>
+          <t>-26,27; 13,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 39,13</t>
+          <t>-24,52; 33,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 8,83</t>
+          <t>-18,82; 10,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,82; -1,89</t>
+          <t>-28,54; -3,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 37,75</t>
+          <t>-20,26; 37,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,24; 5,87</t>
+          <t>-8,98; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 0,9</t>
+          <t>-14,1; 1,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -0,8</t>
+          <t>-14,45; -0,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 10,2</t>
+          <t>-3,48; 10,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 1,07</t>
+          <t>-11,17; 1,2</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 18,21</t>
+          <t>-12,76; 19,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 6,0</t>
+          <t>-4,61; 5,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,81; -0,98</t>
+          <t>-10,41; -0,27</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 6,85</t>
+          <t>-11,23; 8,07</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-44,82; 41,73</t>
+          <t>-42,09; 36,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-64,22; 6,82</t>
+          <t>-63,88; 12,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,56; -5,76</t>
+          <t>-68,09; -1,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 89,92</t>
+          <t>-24,12; 89,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-65,77; 10,22</t>
+          <t>-62,12; 14,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-81,09; 149,55</t>
+          <t>-80,94; 162,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 43,56</t>
+          <t>-24,78; 43,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,47; -5,13</t>
+          <t>-56,04; -0,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-63,81; 49,45</t>
+          <t>-65,11; 61,73</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,92; 4,9</t>
+          <t>-7,95; 5,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,47; -1,64</t>
+          <t>-13,85; -1,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,18; -6,18</t>
+          <t>-18,31; -6,34</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,65</t>
+          <t>-6,78; 4,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,34</t>
+          <t>-6,25; 5,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 6,75</t>
+          <t>-6,41; 7,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 2,91</t>
+          <t>-5,57; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,31; -0,01</t>
+          <t>-8,15; -0,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -0,9</t>
+          <t>-9,8; -0,82</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 25,75</t>
+          <t>-32,24; 27,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,81; -7,44</t>
+          <t>-55,1; -8,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-71,8; -31,9</t>
+          <t>-73,35; -33,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,94; 36,38</t>
+          <t>-36,73; 34,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,47; 35,16</t>
+          <t>-34,96; 40,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,44; 55,16</t>
+          <t>-37,22; 63,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,26; 19,3</t>
+          <t>-26,76; 16,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,15; -0,1</t>
+          <t>-40,29; -0,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,89; -4,59</t>
+          <t>-50,04; -4,42</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-14,48; 0,5</t>
+          <t>-13,94; 0,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,34; -3,19</t>
+          <t>-16,65; -2,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 37,29</t>
+          <t>-1,67; 37,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 5,07</t>
+          <t>-8,47; 4,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 4,35</t>
+          <t>-8,54; 4,81</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 10,69</t>
+          <t>-4,14; 10,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 0,81</t>
+          <t>-9,11; 0,34</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,27; -0,84</t>
+          <t>-10,44; -1,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 25,17</t>
+          <t>-0,15; 23,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,73; 4,28</t>
+          <t>-55,59; 1,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,82; -17,64</t>
+          <t>-66,58; -13,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 217,56</t>
+          <t>-8,16; 255,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-43,38; 42,22</t>
+          <t>-44,61; 41,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 38,21</t>
+          <t>-47,03; 43,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,9; 98,22</t>
+          <t>-22,83; 90,09</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 5,23</t>
+          <t>-43,68; 2,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,07; -5,42</t>
+          <t>-50,34; -6,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,24; 160,52</t>
+          <t>-1,77; 135,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 10,57</t>
+          <t>-1,67; 10,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 10,31</t>
+          <t>-1,13; 10,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 6,91</t>
+          <t>-5,83; 6,44</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 1,59</t>
+          <t>-8,97; 1,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 6,95</t>
+          <t>-4,69; 6,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 4,43</t>
+          <t>-6,31; 5,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 4,73</t>
+          <t>-3,45; 4,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 7,11</t>
+          <t>-1,36; 6,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,71</t>
+          <t>-4,15; 3,99</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,6; 135,95</t>
+          <t>-14,52; 117,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 138,58</t>
+          <t>-8,63; 116,82</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,34; 82,2</t>
+          <t>-40,63; 73,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,59; 18,08</t>
+          <t>-57,71; 18,72</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 74,81</t>
+          <t>-31,34; 72,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,67; 49,4</t>
+          <t>-42,6; 56,92</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 48,23</t>
+          <t>-24,98; 44,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 71,95</t>
+          <t>-9,9; 71,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,42; 37,44</t>
+          <t>-31,9; 40,17</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,6</t>
+          <t>-4,01; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,91</t>
+          <t>-7,21; -0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 11,46</t>
+          <t>-5,4; 10,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,69</t>
+          <t>-3,82; 2,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,9</t>
+          <t>-4,34; 1,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,42</t>
+          <t>-3,83; 4,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,61</t>
+          <t>-3,09; 1,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,52</t>
+          <t>-4,66; -0,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,31</t>
+          <t>-3,31; 6,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 16,09</t>
+          <t>-20,73; 19,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -5,29</t>
+          <t>-37,41; -2,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 72,96</t>
+          <t>-29,22; 75,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 12,94</t>
+          <t>-24,35; 16,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 13,91</t>
+          <t>-27,87; 14,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 33,69</t>
+          <t>-25,47; 35,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 10,63</t>
+          <t>-18,07; 9,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -3,38</t>
+          <t>-27,82; -1,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 37,94</t>
+          <t>-20,18; 41,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-5,1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,27</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-1,83</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,22</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-5,1</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,01</t>
+          <t>-7,7</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,16</t>
+          <t>-5,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 5,26</t>
+          <t>-3,97; 10,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,1; 1,25</t>
+          <t>-11,24; 1,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,45; -0,51</t>
+          <t>-13,28; 17,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 10,58</t>
+          <t>-9,38; 5,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,17; 1,2</t>
+          <t>-13,83; 0,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,76; 19,83</t>
+          <t>-14,94; -0,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 5,78</t>
+          <t>-4,64; 6,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,41; -0,27</t>
+          <t>-10,49; -0,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-11,23; 8,07</t>
+          <t>-11,5; 4,98</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-34,87%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-29,2%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-10,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-34,79%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-42,55%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,01%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-34,87%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-20,58%</t>
+          <t>-43,1%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-31,94%</t>
+          <t>-36,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,09; 36,87</t>
+          <t>-24,13; 94,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 12,74</t>
+          <t>-63,56; 14,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,09; -1,39</t>
+          <t>-84,49; 141,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,12; 89,93</t>
+          <t>-42,4; 43,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-62,12; 14,15</t>
+          <t>-62,14; 10,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,94; 162,9</t>
+          <t>-67,99; -2,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-24,78; 43,88</t>
+          <t>-24,39; 43,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,04; -0,47</t>
+          <t>-56,76; -6,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,11; 61,73</t>
+          <t>-64,78; 49,45</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,82</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-1,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-7,71</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-12,11</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-11,68</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,73</t>
+          <t>-5,81</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 5,11</t>
+          <t>-6,6; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,85; -1,8</t>
+          <t>-6,35; 4,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-18,31; -6,34</t>
+          <t>-6,62; 6,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 4,2</t>
+          <t>-7,82; 5,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 5,05</t>
+          <t>-14,37; -1,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 7,83</t>
+          <t>-17,64; -5,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 2,72</t>
+          <t>-5,75; 2,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,15; -0,03</t>
+          <t>-8,32; -0,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,8; -0,82</t>
+          <t>-10,25; -1,15</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-8,84%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-4,48%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-5,33%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-6,88%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-35,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-56,23%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-8,84%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-4,48%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,89%</t>
+          <t>-54,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-31,33%</t>
+          <t>-31,77%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,24; 27,69</t>
+          <t>-37,07; 34,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,1; -8,55</t>
+          <t>-35,47; 35,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,35; -33,79</t>
+          <t>-37,3; 50,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-36,73; 34,15</t>
+          <t>-31,65; 28,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 40,99</t>
+          <t>-56,81; -9,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-37,22; 63,31</t>
+          <t>-71,29; -24,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 16,85</t>
+          <t>-28,65; 16,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,29; -0,57</t>
+          <t>-40,55; 0,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-50,04; -4,42</t>
+          <t>-51,33; -6,19</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,57</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,87</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,82</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-6,71</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,55</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,69</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,57</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,87</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>2,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7,85</t>
+          <t>2,85</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,94; 0,2</t>
+          <t>-7,7; 4,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,65; -2,78</t>
+          <t>-8,6; 4,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 37,0</t>
+          <t>-4,75; 10,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,66</t>
+          <t>-13,68; 0,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 4,81</t>
+          <t>-15,84; -2,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 10,27</t>
+          <t>-4,54; 12,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 0,34</t>
+          <t>-8,45; 0,59</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,44; -1,0</t>
+          <t>-9,94; -1,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 23,74</t>
+          <t>-2,43; 8,74</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-10,37%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,36%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18,69%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-32,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-45,51%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>60,49%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-10,37%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-12,36%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>15,88%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 1,95</t>
+          <t>-42,76; 39,39</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -13,6</t>
+          <t>-45,15; 40,19</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 255,06</t>
+          <t>-28,78; 89,05</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-44,61; 41,46</t>
+          <t>-55,7; 4,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 43,99</t>
+          <t>-64,14; -12,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 90,09</t>
+          <t>-19,52; 75,41</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-43,68; 2,29</t>
+          <t>-41,61; 4,32</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-50,34; -6,09</t>
+          <t>-47,95; -3,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 135,48</t>
+          <t>-12,02; 56,1</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-3,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,14</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>4,49</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,55</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,8</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-3,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>1,03</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,17</t>
+          <t>-0,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 10,16</t>
+          <t>-8,22; 2,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 10,34</t>
+          <t>-4,15; 6,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 6,44</t>
+          <t>-6,32; 4,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 1,48</t>
+          <t>-1,81; 10,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,7</t>
+          <t>-1,53; 10,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 5,05</t>
+          <t>-4,77; 7,33</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 4,54</t>
+          <t>-3,21; 4,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 6,95</t>
+          <t>-1,35; 7,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,99</t>
+          <t>-4,48; 3,98</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-27,08%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,73%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-9,39%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>39,27%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>39,8%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-27,08%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,73%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-9,0%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,41%</t>
+          <t>-0,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,52; 117,11</t>
+          <t>-56,55; 26,59</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 116,82</t>
+          <t>-27,37; 80,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 73,78</t>
+          <t>-43,9; 50,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,71; 18,72</t>
+          <t>-13,44; 128,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-31,34; 72,97</t>
+          <t>-11,88; 119,58</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-42,6; 56,92</t>
+          <t>-34,55; 85,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,98; 44,28</t>
+          <t>-23,49; 49,35</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 71,89</t>
+          <t>-10,2; 72,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 40,17</t>
+          <t>-33,44; 40,67</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,27</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,47</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-1,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,06</t>
+          <t>-3,85; 2,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,38</t>
+          <t>-4,39; 1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 10,66</t>
+          <t>-3,82; 4,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,03</t>
+          <t>-4,18; 2,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,86</t>
+          <t>-7,21; -0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,88</t>
+          <t>-7,09; 0,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,32</t>
+          <t>-3,22; 1,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,26</t>
+          <t>-5,07; -0,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,28</t>
+          <t>-4,34; 0,86</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-7,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-8,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-3,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-4,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,9%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,02%</t>
+          <t>-19,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,84%</t>
+          <t>-12,13%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 19,6</t>
+          <t>-25,17; 16,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -2,12</t>
+          <t>-28,04; 11,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 75,68</t>
+          <t>-24,67; 35,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 16,78</t>
+          <t>-22,17; 15,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 14,58</t>
+          <t>-38,69; -5,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 35,92</t>
+          <t>-35,94; 2,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 9,02</t>
+          <t>-19,28; 8,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,82; -1,92</t>
+          <t>-28,82; -1,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 41,37</t>
+          <t>-25,61; 6,02</t>
         </is>
       </c>
     </row>
